--- a/WorkBot/refactor-experimental/data/orders/Russo Produce/Russo Produce_Triphammer_20260220.xlsx
+++ b/WorkBot/refactor-experimental/data/orders/Russo Produce/Russo Produce_Triphammer_20260220.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E22"/>
+  <dimension ref="A1:E24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -884,6 +884,48 @@
         <v>60</v>
       </c>
     </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>VASP11</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Asparagus - Fresh</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>2</v>
+      </c>
+      <c r="D23" t="n">
+        <v>42</v>
+      </c>
+      <c r="E23" t="n">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>VPEPPAB</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Pepper - Poblano Fresh</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>2</v>
+      </c>
+      <c r="D24" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="E24" t="n">
+        <v>55</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
